--- a/analysis/main_tables/main_table.xlsx
+++ b/analysis/main_tables/main_table.xlsx
@@ -530,27 +530,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5990826765635748</v>
+        <v>0.4832600257612836</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1451049396052904</v>
+        <v>-0.1171477480323237</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y = 0.599x - 0.145</t>
+          <t>y = 0.483x - 0.117</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.5885366722060511</v>
+        <v>0.5885366722060508</v>
       </c>
       <c r="G3" t="n">
         <v>0.07729454616211583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2422118770611652</v>
+        <v>0.2424114178444199</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4539777369582845</v>
+        <v>0.3661122777289599</v>
       </c>
       <c r="J3" t="n">
         <v>0.09729531263741434</v>
@@ -568,27 +568,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6693714833209766</v>
+        <v>0.4789549017409616</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02322502367856069</v>
+        <v>-0.1103914231048476</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y = 0.669x + 0.023</t>
+          <t>y = 0.479x - 0.110</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.624070185767616</v>
+        <v>0.5914468785146928</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07651912608680006</v>
+        <v>0.07723103900594563</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03469676294444686</v>
+        <v>0.2304839614410122</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6925965069995373</v>
+        <v>0.3685634786361139</v>
       </c>
       <c r="J4" t="n">
         <v>0.09729531263741434</v>
@@ -644,14 +644,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7871438062570995</v>
+        <v>0.6349626703807271</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1946830407481376</v>
+        <v>-0.1579496631228065</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>y = 0.787x - 0.195</t>
+          <t>y = 0.635x - 0.158</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -661,10 +661,10 @@
         <v>0.07949844646981874</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2473284286817466</v>
+        <v>0.2487542504319176</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5924607655089619</v>
+        <v>0.4770130072579205</v>
       </c>
       <c r="J6" t="n">
         <v>0.1230335942309437</v>
@@ -682,27 +682,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.780385435649719</v>
+        <v>0.6294678844678193</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.03514352565799161</v>
+        <v>-0.1493440040719486</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>y = 0.780x - 0.035</t>
+          <t>y = 0.629x - 0.149</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.756115557185981</v>
+        <v>0.7187664039301185</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07823574883004092</v>
+        <v>0.0793933368200274</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04503354887541239</v>
+        <v>0.2372543663577225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7452419099917273</v>
+        <v>0.4801238803958707</v>
       </c>
       <c r="J7" t="n">
         <v>0.1230335942309437</v>
@@ -758,27 +758,27 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8529826036989322</v>
+        <v>0.6880726336504724</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2099476468170498</v>
+        <v>-0.1701417919777667</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>y = 0.853x - 0.210</t>
+          <t>y = 0.688x - 0.170</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7400733070297351</v>
+        <v>0.7400733070297357</v>
       </c>
       <c r="G9" t="n">
         <v>0.08083484371271089</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2461335622867553</v>
+        <v>0.2472730110992838</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6430349568818824</v>
+        <v>0.5179308416727058</v>
       </c>
       <c r="J9" t="n">
         <v>0.1302671269017737</v>
@@ -796,27 +796,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8257978031026181</v>
+        <v>0.6822021167507898</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.077237895314617</v>
+        <v>-0.1609828528661669</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>y = 0.826x - 0.077</t>
+          <t>y = 0.682x - 0.161</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7723375754511835</v>
+        <v>0.7434380683738435</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07969976409868626</v>
+        <v>0.08071646904641239</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09353124339205708</v>
+        <v>0.2359753054313292</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7485599077880011</v>
+        <v>0.5212192638846229</v>
       </c>
       <c r="J10" t="n">
         <v>0.1302671269017737</v>
@@ -872,27 +872,27 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9404384522013414</v>
+        <v>0.7586203514424157</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2347244353821984</v>
+        <v>-0.1908373076128029</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>y = 0.940x - 0.235</t>
+          <t>y = 0.759x - 0.191</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.782231996944451</v>
+        <v>0.7822319969444516</v>
       </c>
       <c r="G12" t="n">
         <v>0.07862700020472366</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2495904275636164</v>
+        <v>0.2515583812772108</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7057140168191429</v>
+        <v>0.5677830438296128</v>
       </c>
       <c r="J12" t="n">
         <v>0.14093043707678</v>
@@ -910,27 +910,27 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9096146551074421</v>
+        <v>0.7523284357116227</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1378048728044031</v>
+        <v>-0.1810058007552863</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>y = 0.910x - 0.138</t>
+          <t>y = 0.752x - 0.181</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.806745011545474</v>
+        <v>0.7857354348774375</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07763520775569017</v>
+        <v>0.07848525169503817</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1514980789179632</v>
+        <v>0.2405941237407491</v>
       </c>
       <c r="I13" t="n">
-        <v>0.771809782303039</v>
+        <v>0.5713226349563363</v>
       </c>
       <c r="J13" t="n">
         <v>0.14093043707678</v>
@@ -986,27 +986,27 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.004054301607032</v>
+        <v>0.8099371366296725</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2364620828859584</v>
+        <v>-0.1896062154776302</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>y = 1.004x - 0.236</t>
+          <t>y = 0.810x - 0.190</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.8036599213638229</v>
+        <v>0.8036599213638219</v>
       </c>
       <c r="G15" t="n">
         <v>0.08309191886343829</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2355072654013738</v>
+        <v>0.2340999157868272</v>
       </c>
       <c r="I15" t="n">
-        <v>0.767592218721074</v>
+        <v>0.6203309211520422</v>
       </c>
       <c r="J15" t="n">
         <v>0.1660500395743601</v>
@@ -1024,27 +1024,27 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9823500619064619</v>
+        <v>0.8032294104731906</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1855439549652754</v>
+        <v>-0.1793615301419243</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>y = 0.982x - 0.186</t>
+          <t>y = 0.803x - 0.179</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.8139452667649676</v>
+        <v>0.8066501015898672</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08263021887197465</v>
+        <v>0.08295769233715304</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1888776335038727</v>
+        <v>0.2233005014548217</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7968061069411865</v>
+        <v>0.6238678803312663</v>
       </c>
       <c r="J16" t="n">
         <v>0.1660500395743601</v>
@@ -1100,27 +1100,27 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7638702021886198</v>
+        <v>0.6161886297654867</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1268213904523227</v>
+        <v>-0.09117411435018735</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>y = 0.764x - 0.127</t>
+          <t>y = 0.616x - 0.091</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>0.7642292533357955</v>
       </c>
       <c r="G18" t="n">
-        <v>0.06029442217092444</v>
+        <v>0.06029442217092446</v>
       </c>
       <c r="H18" t="n">
-        <v>0.166024790715697</v>
+        <v>0.1479646165897073</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6370488117362971</v>
+        <v>0.5250145154152994</v>
       </c>
       <c r="J18" t="n">
         <v>0.1882842318177868</v>
@@ -1138,27 +1138,27 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7629168788216554</v>
+        <v>0.6112626948192624</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1250175382014682</v>
+        <v>-0.08407215585801098</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>y = 0.763x - 0.125</t>
+          <t>y = 0.611x - 0.084</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.7644707871401335</v>
+        <v>0.7656324417913569</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06028782295564297</v>
+        <v>0.06025608408932925</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1638678362897947</v>
+        <v>0.137538502791945</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6378993406201872</v>
+        <v>0.5271905389612515</v>
       </c>
       <c r="J19" t="n">
         <v>0.1882842318177868</v>
@@ -1214,27 +1214,27 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4653191314089975</v>
+        <v>0.3381319021572047</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09111809708896604</v>
+        <v>-0.04148405640533964</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>y = 0.465x - 0.091</t>
+          <t>y = 0.338x - 0.041</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.5310264851532205</v>
+        <v>0.53102648515322</v>
       </c>
       <c r="G21" t="n">
         <v>0.07106507919241614</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1958185059209972</v>
+        <v>0.1226860173224732</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3742010343200315</v>
+        <v>0.2966478457518651</v>
       </c>
       <c r="J21" t="n">
         <v>0.08024303615612118</v>
@@ -1252,27 +1252,27 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.609132729152529</v>
+        <v>0.3374301215844812</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07307883703361051</v>
+        <v>-0.03800818616088122</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>y = 2.609x + 0.073</t>
+          <t>y = 0.337x - 0.038</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.5929073685334815</v>
+        <v>0.5347842749825662</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06999188082721414</v>
+        <v>0.07099990795242518</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.02800886141861675</v>
+        <v>0.1126401697110056</v>
       </c>
       <c r="I22" t="n">
-        <v>2.68221156618614</v>
+        <v>0.2994219354236</v>
       </c>
       <c r="J22" t="n">
         <v>0.08024303615612118</v>
@@ -1328,27 +1328,27 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.8276207383753993</v>
+        <v>0.6014044032194567</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1713241130382146</v>
+        <v>-0.08304456761150539</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>y = 0.828x - 0.171</t>
+          <t>y = 0.601x - 0.083</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.8095504252942273</v>
+        <v>0.8095504252942268</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07443543144589623</v>
+        <v>0.07443543144589622</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2070079990679305</v>
+        <v>0.1380844023870604</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6562966253371847</v>
+        <v>0.5183598356079513</v>
       </c>
       <c r="J24" t="n">
         <v>0.1225311277835489</v>
@@ -1366,27 +1366,27 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.8649654155528481</v>
+        <v>0.6000756819701113</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03982173357265753</v>
+        <v>-0.07743394604061768</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>y = 0.865x - 0.040</t>
+          <t>y = 0.600x - 0.077</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.8591659210976874</v>
+        <v>0.8140975457396832</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07264987319929</v>
+        <v>0.07427179006172348</v>
       </c>
       <c r="H25" t="n">
-        <v>0.04603852692446116</v>
+        <v>0.1290403000274797</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8251436819801906</v>
+        <v>0.5226417359294936</v>
       </c>
       <c r="J25" t="n">
         <v>0.1225311277835489</v>
@@ -1442,27 +1442,27 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.8386400008693096</v>
+        <v>0.6094117339650319</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1641984375980532</v>
+        <v>-0.07474350417199374</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>y = 0.839x - 0.164</t>
+          <t>y = 0.609x - 0.075</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.8256183584309909</v>
+        <v>0.825618358430992</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07320343774613458</v>
+        <v>0.07320343774613459</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1957913257510373</v>
+        <v>0.122648613418859</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6744415632712564</v>
+        <v>0.5346682297930382</v>
       </c>
       <c r="J27" t="n">
         <v>0.1344496767499455</v>
@@ -1480,27 +1480,27 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8333225780816644</v>
+        <v>0.607843265798543</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08112386611094255</v>
+        <v>-0.06911617627998626</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>y = 0.833x - 0.081</t>
+          <t>y = 0.608x - 0.069</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.8497227725840172</v>
+        <v>0.8293843650167247</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07233005170190364</v>
+        <v>0.07306698234117925</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09734989576028567</v>
+        <v>0.1137072337047054</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7521987119707219</v>
+        <v>0.5387270895185567</v>
       </c>
       <c r="J28" t="n">
         <v>0.1344496767499455</v>
@@ -1556,27 +1556,27 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9266406425914915</v>
+        <v>0.6733588669498168</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1584717239578271</v>
+        <v>-0.05963005541473465</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>y = 0.927x - 0.158</t>
+          <t>y = 0.673x - 0.060</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.8624775248763458</v>
+        <v>0.8624775248763452</v>
       </c>
       <c r="G30" t="n">
-        <v>0.07719729761293938</v>
+        <v>0.07719729761293941</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1710174545276115</v>
+        <v>0.08855613008386905</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7681689186336644</v>
+        <v>0.6137288115350822</v>
       </c>
       <c r="J30" t="n">
         <v>0.1795845638119629</v>
@@ -1594,27 +1594,27 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9131192056502373</v>
+        <v>0.6710601490736766</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1088399977314978</v>
+        <v>-0.05332350401802377</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>y = 0.913x - 0.109</t>
+          <t>y = 0.671x - 0.053</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.8691138878060121</v>
+        <v>0.8646703384810646</v>
       </c>
       <c r="G31" t="n">
-        <v>0.07691627394795067</v>
+        <v>0.07710444064861023</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1191958257563888</v>
+        <v>0.07946158640418582</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8042792079187395</v>
+        <v>0.6177366450556528</v>
       </c>
       <c r="J31" t="n">
         <v>0.1795845638119629</v>
@@ -1670,27 +1670,27 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.8560918861505338</v>
+        <v>0.6220934372693879</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.138685940858836</v>
+        <v>-0.04736947300277916</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>y = 0.856x - 0.139</t>
+          <t>y = 0.622x - 0.047</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.841212927430945</v>
+        <v>0.8412129274309452</v>
       </c>
       <c r="G33" t="n">
         <v>0.07476233464372814</v>
       </c>
       <c r="H33" t="n">
-        <v>0.16199889649982</v>
+        <v>0.07614527041259647</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7174059452916978</v>
+        <v>0.5747239642666088</v>
       </c>
       <c r="J33" t="n">
         <v>0.1757301061537291</v>
@@ -1708,27 +1708,27 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.8508086154599527</v>
+        <v>0.620090912117839</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1234640130749899</v>
+        <v>-0.04184108536940623</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>y = 0.851x - 0.123</t>
+          <t>y = 0.620x - 0.042</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.8434796649577093</v>
+        <v>0.8432992926473709</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07467833568148227</v>
+        <v>0.07468501977556347</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1451137316095988</v>
+        <v>0.06747572743245583</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7273446023849628</v>
+        <v>0.5782498267484327</v>
       </c>
       <c r="J34" t="n">
         <v>0.1757301061537291</v>
@@ -1784,27 +1784,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.3853676153219305</v>
+        <v>0.2800338004672694</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.08766525552845314</v>
+        <v>-0.04655937656078055</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>y = 0.385x - 0.088</t>
+          <t>y = 0.280x - 0.047</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.3745277775290248</v>
+        <v>0.3745277775290246</v>
       </c>
       <c r="G36" t="n">
         <v>0.07182983777736945</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2274847497375172</v>
+        <v>0.1662634170699778</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2977023597934774</v>
+        <v>0.2334744239064888</v>
       </c>
       <c r="J36" t="n">
         <v>0.05149094101684386</v>
@@ -1822,27 +1822,27 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>507840.834488432</v>
+        <v>0.2795176237497607</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08013535837177364</v>
+        <v>-0.0433746602947315</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>y = 507840.834x + 0.080</t>
+          <t>y = 0.280x - 0.043</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.496220794737644</v>
+        <v>0.3778776523422254</v>
       </c>
       <c r="G37" t="n">
-        <v>0.06977740038161508</v>
+        <v>0.07177333980817276</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.577962088308577e-07</v>
+        <v>0.1551768354097159</v>
       </c>
       <c r="I37" t="n">
-        <v>507840.9146237904</v>
+        <v>0.2361429634550292</v>
       </c>
       <c r="J37" t="n">
         <v>0.05149094101684386</v>
@@ -1898,27 +1898,27 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.3977270791895768</v>
+        <v>0.289015010877759</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.09108752459720967</v>
+        <v>-0.04866330281698814</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>y = 0.398x - 0.091</t>
+          <t>y = 0.289x - 0.049</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.381057181492149</v>
+        <v>0.3810571814921489</v>
       </c>
       <c r="G39" t="n">
-        <v>0.07202363464535218</v>
+        <v>0.07202363464535219</v>
       </c>
       <c r="H39" t="n">
-        <v>0.229020173287705</v>
+        <v>0.1683763852583097</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3066395545923671</v>
+        <v>0.2403517080607709</v>
       </c>
       <c r="J39" t="n">
         <v>0.05258799584963241</v>
@@ -1936,27 +1936,27 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>371.1051983931052</v>
+        <v>0.2885422960167966</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07179079088517311</v>
+        <v>-0.0455421623664336</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>y = 371.105x + 0.072</t>
+          <t>y = 0.289x - 0.046</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.549336610635078</v>
+        <v>0.3844171117543342</v>
       </c>
       <c r="G40" t="n">
-        <v>0.06905231712819572</v>
+        <v>0.07196430820423395</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.0001934513210702222</v>
+        <v>0.1578353087055996</v>
       </c>
       <c r="I40" t="n">
-        <v>371.1769891839904</v>
+        <v>0.243000133650363</v>
       </c>
       <c r="J40" t="n">
         <v>0.05258799584963241</v>
@@ -2012,27 +2012,27 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.4183426295418958</v>
+        <v>0.3039956441337776</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0961588978903285</v>
+        <v>-0.05153568407252632</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>y = 0.418x - 0.096</t>
+          <t>y = 0.304x - 0.052</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.4301879219231377</v>
+        <v>0.4301879219231376</v>
       </c>
       <c r="G42" t="n">
         <v>0.07050635003272662</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2298567994268881</v>
+        <v>0.1695277056333324</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3221837316515673</v>
+        <v>0.2524599600612513</v>
       </c>
       <c r="J42" t="n">
         <v>0.0545787772368142</v>
@@ -2050,27 +2050,27 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10.2989409674786</v>
+        <v>0.3035408006889746</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0604309775973228</v>
+        <v>-0.04840770965799931</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>y = 10.299x + 0.060</t>
+          <t>y = 0.304x - 0.048</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.5848256037548677</v>
+        <v>0.4338813760968098</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06783051568692694</v>
+        <v>0.07044243888626163</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.005867688511677873</v>
+        <v>0.159476780545231</v>
       </c>
       <c r="I43" t="n">
-        <v>10.35937194507593</v>
+        <v>0.2551330910309753</v>
       </c>
       <c r="J43" t="n">
         <v>0.0545787772368142</v>
@@ -2126,27 +2126,27 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.4871200924961712</v>
+        <v>0.3539739338805509</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1066703595919612</v>
+        <v>-0.05471088305903625</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>y = 0.487x - 0.107</t>
+          <t>y = 0.354x - 0.055</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.5218989987117629</v>
+        <v>0.5218989987117625</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0696855860505106</v>
+        <v>0.06968558605051059</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2189816458716485</v>
+        <v>0.1545618979885071</v>
       </c>
       <c r="I45" t="n">
-        <v>0.38044973290421</v>
+        <v>0.2992630508215146</v>
       </c>
       <c r="J45" t="n">
         <v>0.07069818022188841</v>
@@ -2164,27 +2164,27 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.866546096382967</v>
+        <v>0.3533884572598817</v>
       </c>
       <c r="D46" t="n">
-        <v>0.05638404044587862</v>
+        <v>-0.05118674385996176</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>y = 1.867x + 0.056</t>
+          <t>y = 0.353x - 0.051</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.6113561207258259</v>
+        <v>0.5259638817785133</v>
       </c>
       <c r="G46" t="n">
-        <v>0.06795561670435361</v>
+        <v>0.06960697718245326</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.03020768710461575</v>
+        <v>0.144845545485146</v>
       </c>
       <c r="I46" t="n">
-        <v>1.922930136828846</v>
+        <v>0.30220171339992</v>
       </c>
       <c r="J46" t="n">
         <v>0.07069818022188841</v>
@@ -2240,27 +2240,27 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.6429759828361528</v>
+        <v>0.4672292141942706</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1340901520472701</v>
+        <v>-0.0655060472114137</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>y = 0.643x - 0.134</t>
+          <t>y = 0.467x - 0.066</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.7006157380279142</v>
+        <v>0.7006157380279131</v>
       </c>
       <c r="G48" t="n">
-        <v>0.07034781690958251</v>
+        <v>0.07034781690958253</v>
       </c>
       <c r="H48" t="n">
-        <v>0.208546128668448</v>
+        <v>0.1402010944978641</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5088858307888826</v>
+        <v>0.4017231669828569</v>
       </c>
       <c r="J48" t="n">
         <v>0.09911605076223715</v>
@@ -2278,27 +2278,27 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9538258285793627</v>
+        <v>0.4662072281703645</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03867663923445827</v>
+        <v>-0.06093213704864905</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>y = 0.954x + 0.039</t>
+          <t>y = 0.466x - 0.061</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.7586845960231761</v>
+        <v>0.7049694856586144</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0688903766546794</v>
+        <v>0.07023854444796132</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.04054895356740719</v>
+        <v>0.1306975382766541</v>
       </c>
       <c r="I49" t="n">
-        <v>0.992502467813821</v>
+        <v>0.4052750911217154</v>
       </c>
       <c r="J49" t="n">
         <v>0.09911605076223715</v>
@@ -2354,27 +2354,27 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.7944648142480932</v>
+        <v>0.5773110983536146</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1582232909751798</v>
+        <v>-0.07348037745538333</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>y = 0.794x - 0.158</t>
+          <t>y = 0.577x - 0.073</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.7987559504120979</v>
+        <v>0.7987559504120982</v>
       </c>
       <c r="G51" t="n">
         <v>0.07324930055186388</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1991570779946087</v>
+        <v>0.1272803825613883</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6362415232729135</v>
+        <v>0.5038307208982313</v>
       </c>
       <c r="J51" t="n">
         <v>0.1255702769574647</v>
@@ -2392,27 +2392,27 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.8184070522412461</v>
+        <v>0.5758085218002534</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.03588322026319704</v>
+        <v>-0.06800033294117808</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>y = 0.818x - 0.036</t>
+          <t>y = 0.576x - 0.068</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.8352175076561613</v>
+        <v>0.8025824809338078</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07202381469283513</v>
+        <v>0.07312068950510831</v>
       </c>
       <c r="H52" t="n">
-        <v>0.04384519923787211</v>
+        <v>0.1180953917260141</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7825238319780491</v>
+        <v>0.5078081888590753</v>
       </c>
       <c r="J52" t="n">
         <v>0.1255702769574647</v>
@@ -2468,27 +2468,27 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.8768497055426921</v>
+        <v>0.637177452694356</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.1667529072778909</v>
+        <v>-0.07322227202000367</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>y = 0.877x - 0.167</t>
+          <t>y = 0.637x - 0.073</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.8446767808088257</v>
+        <v>0.8446767808088249</v>
       </c>
       <c r="G54" t="n">
         <v>0.07505040202274707</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1901727356738812</v>
+        <v>0.1149166087255244</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7100967982648012</v>
+        <v>0.5639551806743524</v>
       </c>
       <c r="J54" t="n">
         <v>0.1471454226195276</v>
@@ -2506,27 +2506,27 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.869416747179116</v>
+        <v>0.6354342967558725</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.08176119931705486</v>
+        <v>-0.06729657450078017</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>y = 0.869x - 0.082</t>
+          <t>y = 0.635x - 0.067</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.8662664386832915</v>
+        <v>0.8482410639547229</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0742145230747908</v>
+        <v>0.07491240496584443</v>
       </c>
       <c r="H55" t="n">
-        <v>0.09404143591935035</v>
+        <v>0.1059064246993814</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7876555478620612</v>
+        <v>0.5681377222550923</v>
       </c>
       <c r="J55" t="n">
         <v>0.1471454226195276</v>
@@ -2582,27 +2582,27 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.8915083820869502</v>
+        <v>0.6478294243165168</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.1629372939571492</v>
+        <v>-0.06784306653454114</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>y = 0.892x - 0.163</t>
+          <t>y = 0.648x - 0.068</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.8554446488756218</v>
+        <v>0.8554446488756207</v>
       </c>
       <c r="G57" t="n">
-        <v>0.07373002956964288</v>
+        <v>0.07373002956964289</v>
       </c>
       <c r="H57" t="n">
-        <v>0.182765857541043</v>
+        <v>0.1047236571665728</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7285710881298009</v>
+        <v>0.5799863577819757</v>
       </c>
       <c r="J57" t="n">
         <v>0.1575694389017532</v>
@@ -2620,27 +2620,27 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.8813766183248144</v>
+        <v>0.646063827850067</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1214989855920932</v>
+        <v>-0.06202339389086625</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>y = 0.881x - 0.121</t>
+          <t>y = 0.646x - 0.062</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.8652161582416737</v>
+        <v>0.8587576421472526</v>
       </c>
       <c r="G58" t="n">
-        <v>0.07334387741481165</v>
+        <v>0.07359910614288688</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1378513827868724</v>
+        <v>0.09600196020455755</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7598776327327212</v>
+        <v>0.5840404339592007</v>
       </c>
       <c r="J58" t="n">
         <v>0.1575694389017532</v>
@@ -2696,27 +2696,27 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.8869978118948015</v>
+        <v>0.6445517433102225</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.154845309585795</v>
+        <v>-0.06023220965034953</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>y = 0.887x - 0.155</t>
+          <t>y = 0.645x - 0.060</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.8534228964415241</v>
+        <v>0.8534228964415246</v>
       </c>
       <c r="G60" t="n">
         <v>0.07513563475648484</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1745723692993278</v>
+        <v>0.09344821463210254</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7321525023090065</v>
+        <v>0.584319533659873</v>
       </c>
       <c r="J60" t="n">
         <v>0.1664111261872503</v>
@@ -2734,27 +2734,27 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.8793740855497587</v>
+        <v>0.6426803832232895</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.1296417813025106</v>
+        <v>-0.05450159982667657</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>y = 0.879x - 0.130</t>
+          <t>y = 0.643x - 0.055</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.8584341219557329</v>
+        <v>0.8562413837773374</v>
       </c>
       <c r="G61" t="n">
-        <v>0.07493913472866838</v>
+        <v>0.07502511631377713</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1474250645235496</v>
+        <v>0.08480358394219234</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7497323042472481</v>
+        <v>0.5881787833966129</v>
       </c>
       <c r="J61" t="n">
         <v>0.1664111261872503</v>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.4239497787480961</v>
+        <v>0.4241088223917047</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.002565950749334717</v>
+        <v>-0.002672392594289641</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2783,19 +2783,19 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.6409382230977771</v>
+        <v>0.6412372970886957</v>
       </c>
       <c r="G62" t="n">
-        <v>0.07803030766595925</v>
+        <v>0.07802020755710587</v>
       </c>
       <c r="H62" t="n">
-        <v>0.006052487530272687</v>
+        <v>0.006301195479073135</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4213838279987614</v>
+        <v>0.4214364297974151</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1349180652311648</v>
+        <v>0.1349073854191462</v>
       </c>
     </row>
     <row r="63">
@@ -2810,30 +2810,30 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.6571883236464123</v>
+        <v>0.5610932385381719</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.07570714552882743</v>
+        <v>-0.07300308705943037</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>y = 0.657x - 0.076</t>
+          <t>y = 0.561x - 0.073</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.7604217987621019</v>
+        <v>0.76182750160554</v>
       </c>
       <c r="G63" t="n">
-        <v>0.07134529350853232</v>
+        <v>0.07081018425509757</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1151985554289309</v>
+        <v>0.1301086558263059</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5814811781175849</v>
+        <v>0.4880901514787416</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1349180652311648</v>
+        <v>0.1349073854191462</v>
       </c>
     </row>
     <row r="64">
@@ -2848,30 +2848,30 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.7474851936761759</v>
+        <v>0.5594533277307201</v>
       </c>
       <c r="D64" t="n">
-        <v>0.01832184813714574</v>
+        <v>-0.06745494153047216</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>y = 0.747x + 0.018</t>
+          <t>y = 0.559x - 0.067</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.8387172441999282</v>
+        <v>0.7669477731529121</v>
       </c>
       <c r="G64" t="n">
-        <v>0.06886641041966188</v>
+        <v>0.0706474762101917</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.02451131914337703</v>
+        <v>0.1205729561107196</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7658070418133217</v>
+        <v>0.4919983862002479</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1349180652311648</v>
+        <v>0.1349073854191462</v>
       </c>
     </row>
     <row r="65">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.5497197539314632</v>
+        <v>0.549811321943617</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.03257736857582771</v>
+        <v>-0.03263860220726877</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.7101341576805366</v>
+        <v>0.7102506966638465</v>
       </c>
       <c r="G65" t="n">
-        <v>0.08563169728915801</v>
+        <v>0.08562713546898953</v>
       </c>
       <c r="H65" t="n">
-        <v>0.05926177537343751</v>
+        <v>0.0593632777366048</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5171423853556355</v>
+        <v>0.5171727197363483</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1431310929698081</v>
+        <v>0.1431201458234323</v>
       </c>
     </row>
     <row r="66">
@@ -2924,30 +2924,30 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.8186445272501087</v>
+        <v>0.8636316229808105</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.1044297198695556</v>
+        <v>-0.2916275556923994</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>y = 0.819x - 0.104</t>
+          <t>y = 0.864x - 0.292</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.7940850890904245</v>
+        <v>0.7780498887053863</v>
       </c>
       <c r="G66" t="n">
-        <v>0.07695866535414121</v>
+        <v>0.07711528435831476</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1275641824912007</v>
+        <v>0.3376758654180027</v>
       </c>
       <c r="I66" t="n">
-        <v>0.7142148073805531</v>
+        <v>0.5720040672884111</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1431310929698081</v>
+        <v>0.1431201458234323</v>
       </c>
     </row>
     <row r="67">
@@ -2962,30 +2962,30 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.8905473972314594</v>
+        <v>0.8539584839846307</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.01134672169303777</v>
+        <v>-0.2785636406273009</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>y = 0.891x - 0.011</t>
+          <t>y = 0.854x - 0.279</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.8476824226826389</v>
+        <v>0.7820202634660472</v>
       </c>
       <c r="G67" t="n">
-        <v>0.07461794539998461</v>
+        <v>0.07694139754119492</v>
       </c>
       <c r="H67" t="n">
-        <v>0.01274128892893578</v>
+        <v>0.3262027907112103</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8792006755384216</v>
+        <v>0.5753948433573298</v>
       </c>
       <c r="J67" t="n">
-        <v>0.1431310929698081</v>
+        <v>0.1431201458234323</v>
       </c>
     </row>
     <row r="68">
@@ -3000,30 +3000,30 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.5831687756605118</v>
+        <v>0.5833687986314176</v>
       </c>
       <c r="D68" t="n">
-        <v>0.03062941464382929</v>
+        <v>0.0304956546921597</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>y = 0.583x + 0.031</t>
+          <t>y = 0.583x + 0.030</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.7838582598485035</v>
+        <v>0.7840719584357971</v>
       </c>
       <c r="G68" t="n">
-        <v>0.08983128431400769</v>
+        <v>0.08982329992578182</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.05252238446603667</v>
+        <v>-0.05227508698391561</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6137981903043411</v>
+        <v>0.6138644533235773</v>
       </c>
       <c r="J68" t="n">
-        <v>0.2312223587223648</v>
+        <v>0.2312042320494592</v>
       </c>
     </row>
     <row r="69">
@@ -3038,30 +3038,30 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.8682735314843862</v>
+        <v>0.9226664827582246</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.05519846216489332</v>
+        <v>-0.2583900998488662</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>y = 0.868x - 0.055</t>
+          <t>y = 0.923x - 0.258</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.847207712774909</v>
+        <v>0.8365716961611958</v>
       </c>
       <c r="G69" t="n">
-        <v>0.08033063631815804</v>
+        <v>0.08027701071313023</v>
       </c>
       <c r="H69" t="n">
-        <v>0.06357266479208105</v>
+        <v>0.2800471293553802</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8130750693194929</v>
+        <v>0.6642763829093584</v>
       </c>
       <c r="J69" t="n">
-        <v>0.2312223587223648</v>
+        <v>0.2312042320494592</v>
       </c>
     </row>
     <row r="70">
@@ -3076,30 +3076,30 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.8714038618269381</v>
+        <v>0.9121343742770236</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.02225877082980504</v>
+        <v>-0.2447968741128076</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>y = 0.871x - 0.022</t>
+          <t>y = 0.912x - 0.245</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.8550880163505568</v>
+        <v>0.8390041846626251</v>
       </c>
       <c r="G70" t="n">
-        <v>0.07996776824377196</v>
+        <v>0.08016392111852952</v>
       </c>
       <c r="H70" t="n">
-        <v>0.02554357606717339</v>
+        <v>0.2683780822390764</v>
       </c>
       <c r="I70" t="n">
-        <v>0.849145090997133</v>
+        <v>0.667337500164216</v>
       </c>
       <c r="J70" t="n">
-        <v>0.2312223587223648</v>
+        <v>0.2312042320494592</v>
       </c>
     </row>
     <row r="71">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.489679033322039</v>
+        <v>0.4898371300807023</v>
       </c>
       <c r="D71" t="n">
-        <v>0.05416725219321766</v>
+        <v>0.05406152926198543</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3125,19 +3125,19 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.6610195239634022</v>
+        <v>0.6611963467765015</v>
       </c>
       <c r="G71" t="n">
-        <v>0.08584886838709019</v>
+        <v>0.08584497590277905</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.110617871109859</v>
+        <v>-0.1103663359555422</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5438462855152567</v>
+        <v>0.5438986593426878</v>
       </c>
       <c r="J71" t="n">
-        <v>0.2254935800903592</v>
+        <v>0.2254761055634857</v>
       </c>
     </row>
     <row r="72">
@@ -3152,30 +3152,30 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.7955985759001127</v>
+        <v>0.8461232220523061</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.04188786549879653</v>
+        <v>-0.2285482935813685</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>y = 0.796x - 0.042</t>
+          <t>y = 0.846x - 0.229</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.8164806074401034</v>
+        <v>0.8074786585497478</v>
       </c>
       <c r="G72" t="n">
-        <v>0.07688491321267643</v>
+        <v>0.07673681612953624</v>
       </c>
       <c r="H72" t="n">
-        <v>0.05264949783426402</v>
+        <v>0.2701123047149271</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7537107104013162</v>
+        <v>0.6175749284709375</v>
       </c>
       <c r="J72" t="n">
-        <v>0.2254935800903592</v>
+        <v>0.2254761055634857</v>
       </c>
     </row>
     <row r="73">
@@ -3190,30 +3190,30 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.7957699178953539</v>
+        <v>0.8365964256503772</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.02455020241324579</v>
+        <v>-0.2163335723841607</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>y = 0.796x - 0.025</t>
+          <t>y = 0.837x - 0.216</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.8200198151017841</v>
+        <v>0.8095381824244459</v>
       </c>
       <c r="G73" t="n">
-        <v>0.07674293204164766</v>
+        <v>0.07665339260463401</v>
       </c>
       <c r="H73" t="n">
-        <v>0.03085088021192857</v>
+        <v>0.2585877320907523</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7712197154821081</v>
+        <v>0.6202628532662164</v>
       </c>
       <c r="J73" t="n">
-        <v>0.2254935800903592</v>
+        <v>0.2254761055634857</v>
       </c>
     </row>
   </sheetData>
